--- a/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 19,88</t>
+          <t>8,76; 20,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 16,1</t>
+          <t>3,21; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 11,1</t>
+          <t>-1,33; 12,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 7,89</t>
+          <t>-12,17; 8,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,11; 102,22</t>
+          <t>35,9; 102,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 58,11</t>
+          <t>9,59; 56,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 42,48</t>
+          <t>-4,08; 45,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 41,75</t>
+          <t>-38,87; 45,86</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 20,65</t>
+          <t>10,9; 21,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 14,02</t>
+          <t>3,54; 14,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 16,99</t>
+          <t>6,12; 17,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 3,69</t>
+          <t>-12,95; 3,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,79; 82,86</t>
+          <t>37,69; 90,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 38,32</t>
+          <t>9,01; 39,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 65,75</t>
+          <t>19,6; 66,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 17,72</t>
+          <t>-46,64; 18,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 23,06</t>
+          <t>12,45; 23,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,66; 21,58</t>
+          <t>10,49; 21,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 19,89</t>
+          <t>8,67; 20,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 8,64</t>
+          <t>-3,86; 8,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,6; 75,67</t>
+          <t>34,37; 75,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,3; 56,59</t>
+          <t>23,87; 56,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,66; 65,44</t>
+          <t>24,19; 64,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 46,58</t>
+          <t>-15,89; 44,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 21,78</t>
+          <t>9,85; 21,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 26,18</t>
+          <t>15,23; 26,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 13,53</t>
+          <t>1,92; 13,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 27,98</t>
+          <t>2,99; 26,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 49,42</t>
+          <t>19,77; 50,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,23; 56,29</t>
+          <t>28,24; 56,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 27,85</t>
+          <t>3,21; 27,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 305,78</t>
+          <t>9,92; 236,18</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 12,76</t>
+          <t>0,88; 12,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 16,3</t>
+          <t>5,4; 15,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,68; 21,24</t>
+          <t>8,25; 20,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 10,55</t>
+          <t>0,59; 10,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 19,02</t>
+          <t>1,19; 18,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 22,92</t>
+          <t>6,76; 21,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 35,6</t>
+          <t>12,02; 35,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 25,8</t>
+          <t>1,0; 26,46</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 17,7</t>
+          <t>6,01; 18,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,39</t>
+          <t>-2,4; 5,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,11</t>
+          <t>-3,37; 6,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,08; 43,22</t>
+          <t>10,21; 41,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 24,53</t>
+          <t>7,46; 25,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,95</t>
+          <t>-2,51; 6,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 7,29</t>
+          <t>-3,76; 7,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,08; 98,82</t>
+          <t>20,72; 96,95</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 9,22</t>
+          <t>-2,35; 8,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,25</t>
+          <t>-1,13; 5,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 7,19</t>
+          <t>-0,46; 6,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 8,91</t>
+          <t>-1,97; 9,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 11,19</t>
+          <t>-2,63; 10,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 5,71</t>
+          <t>-1,16; 5,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,93</t>
+          <t>-0,49; 7,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 15,01</t>
+          <t>-2,94; 15,32</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,43</t>
+          <t>13,69; 18,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,1</t>
+          <t>11,39; 16,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,95</t>
+          <t>9,39; 13,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,45; 22,02</t>
+          <t>4,72; 23,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 42,9</t>
+          <t>29,99; 43,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,88; 30,53</t>
+          <t>20,51; 30,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 28,53</t>
+          <t>18,25; 29,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,84; 78,75</t>
+          <t>14,02; 81,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,82%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 20,05</t>
+          <t>8,76; 20,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 15,88</t>
+          <t>3,02; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 12,0</t>
+          <t>-1,81; 11,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 8,43</t>
+          <t>-6,88; 11,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,9; 102,28</t>
+          <t>34,67; 103,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 56,41</t>
+          <t>8,28; 56,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 45,52</t>
+          <t>-5,23; 43,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 45,86</t>
+          <t>-27,88; 69,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-12,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 21,93</t>
+          <t>10,37; 21,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 14,09</t>
+          <t>3,66; 14,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 17,17</t>
+          <t>5,92; 16,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 3,73</t>
+          <t>-5,51; 6,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,69; 90,49</t>
+          <t>34,27; 84,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 39,35</t>
+          <t>8,86; 40,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 66,0</t>
+          <t>19,22; 66,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 18,36</t>
+          <t>-22,81; 39,51</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 23,11</t>
+          <t>12,58; 23,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 21,51</t>
+          <t>10,23; 20,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 20,07</t>
+          <t>9,58; 19,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,32</t>
+          <t>1,1; 10,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,37; 75,51</t>
+          <t>33,8; 74,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,87; 56,95</t>
+          <t>22,72; 54,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,19; 64,96</t>
+          <t>25,78; 63,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 44,32</t>
+          <t>4,7; 59,69</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 21,96</t>
+          <t>9,3; 21,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,23; 26,32</t>
+          <t>14,73; 26,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 13,27</t>
+          <t>1,26; 12,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 26,94</t>
+          <t>1,49; 10,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 50,82</t>
+          <t>18,05; 49,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,24; 56,21</t>
+          <t>27,67; 56,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 27,01</t>
+          <t>2,61; 26,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 236,18</t>
+          <t>4,53; 37,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 12,6</t>
+          <t>-0,08; 12,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 15,59</t>
+          <t>5,23; 16,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 20,87</t>
+          <t>8,51; 20,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 10,93</t>
+          <t>1,9; 11,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 18,62</t>
+          <t>0,1; 18,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 21,69</t>
+          <t>6,71; 22,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 35,14</t>
+          <t>12,75; 34,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 26,46</t>
+          <t>4,05; 28,99</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,01; 18,13</t>
+          <t>5,95; 18,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,76</t>
+          <t>-2,14; 5,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 6,53</t>
+          <t>-3,68; 6,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 41,64</t>
+          <t>7,4; 18,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 25,09</t>
+          <t>7,36; 24,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,44</t>
+          <t>-2,3; 6,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 7,78</t>
+          <t>-4,12; 7,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,72; 96,95</t>
+          <t>14,21; 42,36</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,84</t>
+          <t>-2,15; 8,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,23</t>
+          <t>-1,43; 5,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,81</t>
+          <t>-0,76; 6,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 9,18</t>
+          <t>-2,52; 8,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 10,64</t>
+          <t>-2,42; 10,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 5,67</t>
+          <t>-1,45; 5,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,59</t>
+          <t>-0,79; 7,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 15,32</t>
+          <t>-3,81; 14,83</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,36</t>
+          <t>13,65; 18,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 16,26</t>
+          <t>11,34; 16,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,98</t>
+          <t>9,13; 13,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 23,1</t>
+          <t>4,73; 9,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,99; 43,08</t>
+          <t>29,81; 42,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,51; 30,79</t>
+          <t>20,6; 30,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,25; 29,04</t>
+          <t>17,98; 29,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,02; 81,34</t>
+          <t>13,9; 28,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
